--- a/쿼리분석/소스프로그램_분석_요약.xlsx
+++ b/쿼리분석/소스프로그램_분석_요약.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F17"/>
+  <dimension ref="A2:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -977,6 +977,46 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>p190872_local_chk_v08_3cha.py</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>&lt;검색기준테이블&gt;
+&lt;검색기준소스테이블&gt;
+[--where &lt;old/new/all&gt;]
+[--db]
+[--conf &lt;경로&gt;]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>- &lt;검색기준테이블&gt;: DB 내 검색 대상 기준 테이블 (필수)
+- &lt;검색기준소스테이블&gt;: DB 내 local_file, id, mid, source_file 정보를 지닌 대상 소스 테이블 (필수)
+- --where: 검색기준테이블 조회 조건 필터 (old, new, all 중 선택, 기본값 all)
+- --db: 분석 결과 DB 테이블 적재 활성화 여부 (선택)
+- --conf: DB 접속 정보 설정 파일 경로 (선택)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>- --where: 'old', 'new', 'all' 중 선택하여 기준 테이블 조회 필터링 (old: asis_enc_yn='Y', new: asis_enc_yn='N')
+- --db: 지정 시 분석 결과를 &lt;검색기준소스테이블명&gt;_work 테이블에 자동 적재
+- --conf: 기본 mysql.conf 경로 재지정</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>3차 암호화 대상 검출 최종 프로그램. 검색기준테이블의 column_name 기준으로 중복 없이 기준 칼럼을 추출하여, 소스테이블에 등록된 local_file 파일 소스 전체를 파싱/완전일치 매칭함. vscode_open_cmd에서 [code] 접두사를 제거하여 vscode 이동 명령어를 기록하고, source_file 컬럼을 함께 로드하여 결과 파일 및 DB에 적재함. 매칭 결과가 없는 파일도 ID별로 기본 행(line_number: 1)을 생성하며, 화면 콘솔에는 상위 10개 매칭 결과만 제한 출력함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F3"/>
